--- a/forcings/Sea_level.xlsx
+++ b/forcings/Sea_level.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\earbmi\Desktop\SCION-main\SCION-main\forcings\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\桌面\MODEL_Wenli0608\20240617-SCION-main\forcings\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B8103BA-C40E-4B56-8FC5-11F365F5DD1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F338039-21F8-4E19-892B-71AFE261A60C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="36930" yWindow="1485" windowWidth="27045" windowHeight="18960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,17 +24,13 @@
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -46,7 +42,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -78,7 +74,7 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -357,13 +353,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B542"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="7.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.75" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1">
         <v>1000</v>
       </c>
@@ -371,7 +367,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>540</v>
       </c>
@@ -379,7 +375,7 @@
         <v>48.1072329661135</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>539</v>
       </c>
@@ -387,7 +383,7 @@
         <v>52.675519189398983</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>538</v>
       </c>
@@ -395,7 +391,7 @@
         <v>57.319121954981462</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>537</v>
       </c>
@@ -403,7 +399,7 @@
         <v>57.62153559553461</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>536</v>
       </c>
@@ -411,7 +407,7 @@
         <v>60.127263527509292</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>535</v>
       </c>
@@ -419,7 +415,7 @@
         <v>66.274431581354477</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>534</v>
       </c>
@@ -427,7 +423,7 @@
         <v>70.771109555255634</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>533</v>
       </c>
@@ -435,7 +431,7 @@
         <v>75.205403553021625</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>532</v>
       </c>
@@ -443,7 +439,7 @@
         <v>75.434953432483653</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>531</v>
       </c>
@@ -451,7 +447,7 @@
         <v>81.902872425107631</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>530</v>
       </c>
@@ -459,7 +455,7 @@
         <v>84.284721768758914</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>529</v>
       </c>
@@ -467,7 +463,7 @@
         <v>85.893021586335863</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>528</v>
       </c>
@@ -475,7 +471,7 @@
         <v>85.618018371859961</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>527</v>
       </c>
@@ -483,7 +479,7 @@
         <v>84.904582289398235</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>526</v>
       </c>
@@ -491,7 +487,7 @@
         <v>88.84803537918792</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>525</v>
       </c>
@@ -499,7 +495,7 @@
         <v>88.720322301826371</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>524</v>
       </c>
@@ -507,7 +503,7 @@
         <v>89.058372741715829</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>523</v>
       </c>
@@ -515,7 +511,7 @@
         <v>84.113799688048545</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>522</v>
       </c>
@@ -523,7 +519,7 @@
         <v>75.100875541823058</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>521</v>
       </c>
@@ -531,7 +527,7 @@
         <v>64.757076951163</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>520</v>
       </c>
@@ -539,7 +535,7 @@
         <v>62.100311363655678</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>519</v>
       </c>
@@ -547,7 +543,7 @@
         <v>59.032581926543216</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>518</v>
       </c>
@@ -555,7 +551,7 @@
         <v>56.323472188146809</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>517</v>
       </c>
@@ -563,7 +559,7 @@
         <v>53.645247590707086</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>516</v>
       </c>
@@ -571,7 +567,7 @@
         <v>47.683692547907903</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>515</v>
       </c>
@@ -579,7 +575,7 @@
         <v>47.594085306587857</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>514</v>
       </c>
@@ -587,7 +583,7 @@
         <v>46.297633201818364</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>513</v>
       </c>
@@ -595,7 +591,7 @@
         <v>46.266379270766386</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>512</v>
       </c>
@@ -603,7 +599,7 @@
         <v>45.316279319164082</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>511</v>
       </c>
@@ -611,7 +607,7 @@
         <v>46.390996544666443</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>510</v>
       </c>
@@ -619,7 +615,7 @@
         <v>46.228442371338467</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>509</v>
       </c>
@@ -627,7 +623,7 @@
         <v>45.000861496657961</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>508</v>
       </c>
@@ -635,7 +631,7 @@
         <v>45.669063819251555</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>507</v>
       </c>
@@ -643,7 +639,7 @@
         <v>46.333986829552849</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>506</v>
       </c>
@@ -651,7 +647,7 @@
         <v>46.756147156179502</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>505</v>
       </c>
@@ -659,7 +655,7 @@
         <v>46.064490923220916</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>504</v>
       </c>
@@ -667,7 +663,7 @@
         <v>44.178617203998797</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>503</v>
       </c>
@@ -675,7 +671,7 @@
         <v>43.64912008083563</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>502</v>
       </c>
@@ -683,7 +679,7 @@
         <v>43.247764898725585</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>501</v>
       </c>
@@ -691,7 +687,7 @@
         <v>43.041161170250739</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>500</v>
       </c>
@@ -699,7 +695,7 @@
         <v>43.030107436079653</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>499</v>
       </c>
@@ -707,7 +703,7 @@
         <v>42.999030847911413</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>498</v>
       </c>
@@ -715,7 +711,7 @@
         <v>43.144387182570902</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>497</v>
       </c>
@@ -723,7 +719,7 @@
         <v>41.78166052963708</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>496</v>
       </c>
@@ -731,7 +727,7 @@
         <v>42.338585719123444</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>495</v>
       </c>
@@ -739,7 +735,7 @@
         <v>43.233551293837039</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>494</v>
       </c>
@@ -747,7 +743,7 @@
         <v>46.21252289124584</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>493</v>
       </c>
@@ -755,7 +751,7 @@
         <v>48.908030347616403</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>492</v>
       </c>
@@ -763,7 +759,7 @@
         <v>50.027219818903639</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>491</v>
       </c>
@@ -771,7 +767,7 @@
         <v>52.14222975691488</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>490</v>
       </c>
@@ -779,7 +775,7 @@
         <v>53.983921175009399</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>489</v>
       </c>
@@ -787,7 +783,7 @@
         <v>55.989959010503412</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>488</v>
       </c>
@@ -795,7 +791,7 @@
         <v>58.056507900106155</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>487</v>
       </c>
@@ -803,7 +799,7 @@
         <v>61.383078971033136</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>486</v>
       </c>
@@ -811,7 +807,7 @@
         <v>61.93989328235147</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>485</v>
       </c>
@@ -819,7 +815,7 @@
         <v>62.499462852556242</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>484</v>
       </c>
@@ -827,7 +823,7 @@
         <v>64.21266259369466</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>483</v>
       </c>
@@ -835,7 +831,7 @@
         <v>64.5691197558223</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>482</v>
       </c>
@@ -843,7 +839,7 @@
         <v>66.158933071202483</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>481</v>
       </c>
@@ -851,7 +847,7 @@
         <v>67.457867805567773</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>480</v>
       </c>
@@ -859,7 +855,7 @@
         <v>67.47567715247655</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>479</v>
       </c>
@@ -867,7 +863,7 @@
         <v>67.282384457650394</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
         <v>478</v>
       </c>
@@ -875,7 +871,7 @@
         <v>68.817250153147143</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>477</v>
       </c>
@@ -883,7 +879,7 @@
         <v>68.461321204829318</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>476</v>
       </c>
@@ -891,7 +887,7 @@
         <v>70.321167939045182</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>475</v>
       </c>
@@ -899,7 +895,7 @@
         <v>72.17372994173293</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>474</v>
       </c>
@@ -907,7 +903,7 @@
         <v>74.052124673395383</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>473</v>
       </c>
@@ -915,7 +911,7 @@
         <v>76.05433069258595</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>472</v>
       </c>
@@ -923,7 +919,7 @@
         <v>76.661084640771776</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>471</v>
       </c>
@@ -931,7 +927,7 @@
         <v>77.448581561289615</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>470</v>
       </c>
@@ -939,7 +935,7 @@
         <v>79.954946430615479</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>469</v>
       </c>
@@ -947,7 +943,7 @@
         <v>80.321221193768793</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>468</v>
       </c>
@@ -955,7 +951,7 @@
         <v>78.193412850349574</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>467</v>
       </c>
@@ -963,7 +959,7 @@
         <v>78.276270378602533</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>466</v>
       </c>
@@ -971,7 +967,7 @@
         <v>78.71934124512687</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>465</v>
       </c>
@@ -979,7 +975,7 @@
         <v>82.100863233453381</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>464</v>
       </c>
@@ -987,7 +983,7 @@
         <v>84.097048683898208</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>463</v>
       </c>
@@ -995,7 +991,7 @@
         <v>87.915191989789051</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>462</v>
       </c>
@@ -1003,7 +999,7 @@
         <v>92.579143478331616</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>461</v>
       </c>
@@ -1011,7 +1007,7 @@
         <v>94.597909078946813</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>460</v>
       </c>
@@ -1019,7 +1015,7 @@
         <v>95.633176357269633</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>459</v>
       </c>
@@ -1027,7 +1023,7 @@
         <v>95.00830389455254</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
         <v>458</v>
       </c>
@@ -1035,7 +1031,7 @@
         <v>94.194934095168961</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>457</v>
       </c>
@@ -1043,7 +1039,7 @@
         <v>97.502012831823706</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>456</v>
       </c>
@@ -1051,7 +1047,7 @@
         <v>99.296810555684146</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>455</v>
       </c>
@@ -1059,7 +1055,7 @@
         <v>102.44183590299757</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>454</v>
       </c>
@@ -1067,7 +1063,7 @@
         <v>107.53719923020049</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>453</v>
       </c>
@@ -1075,7 +1071,7 @@
         <v>107.8672887425117</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>452</v>
       </c>
@@ -1083,7 +1079,7 @@
         <v>112.60971693760278</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>451</v>
       </c>
@@ -1091,7 +1087,7 @@
         <v>113.00251856895474</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>450</v>
       </c>
@@ -1099,7 +1095,7 @@
         <v>110.59638686833088</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
         <v>449</v>
       </c>
@@ -1107,7 +1103,7 @@
         <v>109.43832094401101</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>448</v>
       </c>
@@ -1115,7 +1111,7 @@
         <v>100.95500617283729</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>447</v>
       </c>
@@ -1123,7 +1119,7 @@
         <v>87.536817715598588</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>446</v>
       </c>
@@ -1131,7 +1127,7 @@
         <v>76.797548425985269</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>445</v>
       </c>
@@ -1139,7 +1135,7 @@
         <v>70.339650982786381</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>444</v>
       </c>
@@ -1147,7 +1143,7 @@
         <v>70.001654416086808</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>443</v>
       </c>
@@ -1155,7 +1151,7 @@
         <v>80.41144187631788</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>442</v>
       </c>
@@ -1163,7 +1159,7 @@
         <v>92.612356358598731</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>441</v>
       </c>
@@ -1171,7 +1167,7 @@
         <v>103.94269305238424</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>440</v>
       </c>
@@ -1179,7 +1175,7 @@
         <v>108.11841404175361</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>439</v>
       </c>
@@ -1187,7 +1183,7 @@
         <v>109.07143942712207</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>438</v>
       </c>
@@ -1195,7 +1191,7 @@
         <v>108.31073959421499</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>437</v>
       </c>
@@ -1203,7 +1199,7 @@
         <v>106.3529595547014</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
         <v>436</v>
       </c>
@@ -1211,7 +1207,7 @@
         <v>104.3940205328545</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>435</v>
       </c>
@@ -1219,7 +1215,7 @@
         <v>104.54447922727769</v>
       </c>
     </row>
-    <row r="108" spans="1:2">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>434</v>
       </c>
@@ -1227,7 +1223,7 @@
         <v>105.47439577325254</v>
       </c>
     </row>
-    <row r="109" spans="1:2">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>433</v>
       </c>
@@ -1235,7 +1231,7 @@
         <v>102.94785608891108</v>
       </c>
     </row>
-    <row r="110" spans="1:2">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>432</v>
       </c>
@@ -1243,7 +1239,7 @@
         <v>100.35971507255067</v>
       </c>
     </row>
-    <row r="111" spans="1:2">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>431</v>
       </c>
@@ -1251,7 +1247,7 @@
         <v>93.562798142926596</v>
       </c>
     </row>
-    <row r="112" spans="1:2">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>430</v>
       </c>
@@ -1259,7 +1255,7 @@
         <v>90.390833861274785</v>
       </c>
     </row>
-    <row r="113" spans="1:2">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>429</v>
       </c>
@@ -1267,7 +1263,7 @@
         <v>87.501386936770871</v>
       </c>
     </row>
-    <row r="114" spans="1:2">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>428</v>
       </c>
@@ -1275,7 +1271,7 @@
         <v>89.09105924324875</v>
       </c>
     </row>
-    <row r="115" spans="1:2">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>427</v>
       </c>
@@ -1283,7 +1279,7 @@
         <v>86.864007890766928</v>
       </c>
     </row>
-    <row r="116" spans="1:2">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>426</v>
       </c>
@@ -1291,7 +1287,7 @@
         <v>82.654256829649356</v>
       </c>
     </row>
-    <row r="117" spans="1:2">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>425</v>
       </c>
@@ -1299,7 +1295,7 @@
         <v>72.964249445114191</v>
       </c>
     </row>
-    <row r="118" spans="1:2">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>424</v>
       </c>
@@ -1307,7 +1303,7 @@
         <v>67.46920812151825</v>
       </c>
     </row>
-    <row r="119" spans="1:2">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>423</v>
       </c>
@@ -1315,7 +1311,7 @@
         <v>69.626722874511472</v>
       </c>
     </row>
-    <row r="120" spans="1:2">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>422</v>
       </c>
@@ -1323,7 +1319,7 @@
         <v>69.844458472273331</v>
       </c>
     </row>
-    <row r="121" spans="1:2">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>421</v>
       </c>
@@ -1331,7 +1327,7 @@
         <v>69.676162528426559</v>
       </c>
     </row>
-    <row r="122" spans="1:2">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>420</v>
       </c>
@@ -1339,7 +1335,7 @@
         <v>76.035551133525942</v>
       </c>
     </row>
-    <row r="123" spans="1:2">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>419</v>
       </c>
@@ -1347,7 +1343,7 @@
         <v>75.775925379914028</v>
       </c>
     </row>
-    <row r="124" spans="1:2">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>418</v>
       </c>
@@ -1355,7 +1351,7 @@
         <v>79.242253561208742</v>
       </c>
     </row>
-    <row r="125" spans="1:2">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>417</v>
       </c>
@@ -1363,7 +1359,7 @@
         <v>80.532431117129804</v>
       </c>
     </row>
-    <row r="126" spans="1:2">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>416</v>
       </c>
@@ -1371,7 +1367,7 @@
         <v>85.997358754032874</v>
       </c>
     </row>
-    <row r="127" spans="1:2">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>415</v>
       </c>
@@ -1379,7 +1375,7 @@
         <v>92.405731609884057</v>
       </c>
     </row>
-    <row r="128" spans="1:2">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>414</v>
       </c>
@@ -1387,7 +1383,7 @@
         <v>99.364986610562013</v>
       </c>
     </row>
-    <row r="129" spans="1:2">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>413</v>
       </c>
@@ -1395,7 +1391,7 @@
         <v>104.28665188167953</v>
       </c>
     </row>
-    <row r="130" spans="1:2">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>412</v>
       </c>
@@ -1403,7 +1399,7 @@
         <v>107.33582533963599</v>
       </c>
     </row>
-    <row r="131" spans="1:2">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>411</v>
       </c>
@@ -1411,7 +1407,7 @@
         <v>106.4684564439175</v>
       </c>
     </row>
-    <row r="132" spans="1:2">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>410</v>
       </c>
@@ -1419,7 +1415,7 @@
         <v>106.20599073815141</v>
       </c>
     </row>
-    <row r="133" spans="1:2">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>409</v>
       </c>
@@ -1427,7 +1423,7 @@
         <v>100.35212923804531</v>
       </c>
     </row>
-    <row r="134" spans="1:2">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
         <v>408</v>
       </c>
@@ -1435,7 +1431,7 @@
         <v>97.777583166152709</v>
       </c>
     </row>
-    <row r="135" spans="1:2">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>407</v>
       </c>
@@ -1443,7 +1439,7 @@
         <v>98.806155295513506</v>
       </c>
     </row>
-    <row r="136" spans="1:2">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>406</v>
       </c>
@@ -1451,7 +1447,7 @@
         <v>107.45167460312665</v>
       </c>
     </row>
-    <row r="137" spans="1:2">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>405</v>
       </c>
@@ -1459,7 +1455,7 @@
         <v>118.2458161177444</v>
       </c>
     </row>
-    <row r="138" spans="1:2">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>404</v>
       </c>
@@ -1467,7 +1463,7 @@
         <v>124.21116232192418</v>
       </c>
     </row>
-    <row r="139" spans="1:2">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>403</v>
       </c>
@@ -1475,7 +1471,7 @@
         <v>124.94251916480972</v>
       </c>
     </row>
-    <row r="140" spans="1:2">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>402</v>
       </c>
@@ -1483,7 +1479,7 @@
         <v>123.3814840986973</v>
       </c>
     </row>
-    <row r="141" spans="1:2">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>401</v>
       </c>
@@ -1491,7 +1487,7 @@
         <v>119.29079247363298</v>
       </c>
     </row>
-    <row r="142" spans="1:2">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>400</v>
       </c>
@@ -1499,7 +1495,7 @@
         <v>106.48236875491806</v>
       </c>
     </row>
-    <row r="143" spans="1:2">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
         <v>399</v>
       </c>
@@ -1507,7 +1503,7 @@
         <v>104.23724860422281</v>
       </c>
     </row>
-    <row r="144" spans="1:2">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>398</v>
       </c>
@@ -1515,7 +1511,7 @@
         <v>102.04342433326141</v>
       </c>
     </row>
-    <row r="145" spans="1:2">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>397</v>
       </c>
@@ -1523,7 +1519,7 @@
         <v>108.76704251368521</v>
       </c>
     </row>
-    <row r="146" spans="1:2">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>396</v>
       </c>
@@ -1531,7 +1527,7 @@
         <v>115.06731960099157</v>
       </c>
     </row>
-    <row r="147" spans="1:2">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>395</v>
       </c>
@@ -1539,7 +1535,7 @@
         <v>119.41064959398383</v>
       </c>
     </row>
-    <row r="148" spans="1:2">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
         <v>394</v>
       </c>
@@ -1547,7 +1543,7 @@
         <v>118.57635229815051</v>
       </c>
     </row>
-    <row r="149" spans="1:2">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>393</v>
       </c>
@@ -1555,7 +1551,7 @@
         <v>121.04158233374203</v>
       </c>
     </row>
-    <row r="150" spans="1:2">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>392</v>
       </c>
@@ -1563,7 +1559,7 @@
         <v>122.58061812805778</v>
       </c>
     </row>
-    <row r="151" spans="1:2">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>391</v>
       </c>
@@ -1571,7 +1567,7 @@
         <v>123.6818184446697</v>
       </c>
     </row>
-    <row r="152" spans="1:2">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>390</v>
       </c>
@@ -1579,7 +1575,7 @@
         <v>118.1011863165231</v>
       </c>
     </row>
-    <row r="153" spans="1:2">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>389</v>
       </c>
@@ -1587,7 +1583,7 @@
         <v>112.79689940799028</v>
       </c>
     </row>
-    <row r="154" spans="1:2">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>388</v>
       </c>
@@ -1595,7 +1591,7 @@
         <v>112.47264185421507</v>
       </c>
     </row>
-    <row r="155" spans="1:2">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>387</v>
       </c>
@@ -1603,7 +1599,7 @@
         <v>116.46578628424257</v>
       </c>
     </row>
-    <row r="156" spans="1:2">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>386</v>
       </c>
@@ -1611,7 +1607,7 @@
         <v>125.77061646520707</v>
       </c>
     </row>
-    <row r="157" spans="1:2">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>385</v>
       </c>
@@ -1619,7 +1615,7 @@
         <v>128.00888466842792</v>
       </c>
     </row>
-    <row r="158" spans="1:2">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>384</v>
       </c>
@@ -1627,7 +1623,7 @@
         <v>127.33917259569161</v>
       </c>
     </row>
-    <row r="159" spans="1:2">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>383</v>
       </c>
@@ -1635,7 +1631,7 @@
         <v>122.83911394244662</v>
       </c>
     </row>
-    <row r="160" spans="1:2">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>382</v>
       </c>
@@ -1643,7 +1639,7 @@
         <v>114.33161890262203</v>
       </c>
     </row>
-    <row r="161" spans="1:2">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>381</v>
       </c>
@@ -1651,7 +1647,7 @@
         <v>108.48095379403871</v>
       </c>
     </row>
-    <row r="162" spans="1:2">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>380</v>
       </c>
@@ -1659,7 +1655,7 @@
         <v>103.10515306565641</v>
       </c>
     </row>
-    <row r="163" spans="1:2">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>379</v>
       </c>
@@ -1667,7 +1663,7 @@
         <v>104.90041970812507</v>
       </c>
     </row>
-    <row r="164" spans="1:2">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>378</v>
       </c>
@@ -1675,7 +1671,7 @@
         <v>108.41473443234382</v>
       </c>
     </row>
-    <row r="165" spans="1:2">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>377</v>
       </c>
@@ -1683,7 +1679,7 @@
         <v>111.74789128829073</v>
       </c>
     </row>
-    <row r="166" spans="1:2">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>376</v>
       </c>
@@ -1691,7 +1687,7 @@
         <v>113.02700054765261</v>
       </c>
     </row>
-    <row r="167" spans="1:2">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>375</v>
       </c>
@@ -1699,7 +1695,7 @@
         <v>114.05138121768273</v>
       </c>
     </row>
-    <row r="168" spans="1:2">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>374</v>
       </c>
@@ -1707,7 +1703,7 @@
         <v>113.47093732778808</v>
       </c>
     </row>
-    <row r="169" spans="1:2">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>373</v>
       </c>
@@ -1715,7 +1711,7 @@
         <v>114.08231555532383</v>
       </c>
     </row>
-    <row r="170" spans="1:2">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>372</v>
       </c>
@@ -1723,7 +1719,7 @@
         <v>113.85435820787026</v>
       </c>
     </row>
-    <row r="171" spans="1:2">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>371</v>
       </c>
@@ -1731,7 +1727,7 @@
         <v>113.43823653613126</v>
       </c>
     </row>
-    <row r="172" spans="1:2">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>370</v>
       </c>
@@ -1739,7 +1735,7 @@
         <v>112.82164347233292</v>
       </c>
     </row>
-    <row r="173" spans="1:2">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>369</v>
       </c>
@@ -1747,7 +1743,7 @@
         <v>112.12929527602681</v>
       </c>
     </row>
-    <row r="174" spans="1:2">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>368</v>
       </c>
@@ -1755,7 +1751,7 @@
         <v>111.02784761876934</v>
       </c>
     </row>
-    <row r="175" spans="1:2">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>367</v>
       </c>
@@ -1763,7 +1759,7 @@
         <v>108.92733270431195</v>
       </c>
     </row>
-    <row r="176" spans="1:2">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>366</v>
       </c>
@@ -1771,7 +1767,7 @@
         <v>104.63045424771792</v>
       </c>
     </row>
-    <row r="177" spans="1:2">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>365</v>
       </c>
@@ -1779,7 +1775,7 @@
         <v>101.26791637856277</v>
       </c>
     </row>
-    <row r="178" spans="1:2">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>364</v>
       </c>
@@ -1787,7 +1783,7 @@
         <v>99.957329621497394</v>
       </c>
     </row>
-    <row r="179" spans="1:2">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>363</v>
       </c>
@@ -1795,7 +1791,7 @@
         <v>98.9632479050142</v>
       </c>
     </row>
-    <row r="180" spans="1:2">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>362</v>
       </c>
@@ -1803,7 +1799,7 @@
         <v>98.224780275727156</v>
       </c>
     </row>
-    <row r="181" spans="1:2">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>361</v>
       </c>
@@ -1811,7 +1807,7 @@
         <v>97.776882382542709</v>
       </c>
     </row>
-    <row r="182" spans="1:2">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>360</v>
       </c>
@@ -1819,7 +1815,7 @@
         <v>97.186123259932657</v>
       </c>
     </row>
-    <row r="183" spans="1:2">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>359</v>
       </c>
@@ -1827,7 +1823,7 @@
         <v>94.398011950189954</v>
       </c>
     </row>
-    <row r="184" spans="1:2">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>358</v>
       </c>
@@ -1835,7 +1831,7 @@
         <v>96.421192376147815</v>
       </c>
     </row>
-    <row r="185" spans="1:2">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>357</v>
       </c>
@@ -1843,7 +1839,7 @@
         <v>98.627978687083271</v>
       </c>
     </row>
-    <row r="186" spans="1:2">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>356</v>
       </c>
@@ -1851,7 +1847,7 @@
         <v>101.28663898661853</v>
       </c>
     </row>
-    <row r="187" spans="1:2">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>355</v>
       </c>
@@ -1859,7 +1855,7 @@
         <v>103.67341281150263</v>
       </c>
     </row>
-    <row r="188" spans="1:2">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>354</v>
       </c>
@@ -1867,7 +1863,7 @@
         <v>103.24256666938325</v>
       </c>
     </row>
-    <row r="189" spans="1:2">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>353</v>
       </c>
@@ -1875,7 +1871,7 @@
         <v>104.56664455877014</v>
       </c>
     </row>
-    <row r="190" spans="1:2">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>352</v>
       </c>
@@ -1883,7 +1879,7 @@
         <v>104.21475755902634</v>
       </c>
     </row>
-    <row r="191" spans="1:2">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>351</v>
       </c>
@@ -1891,7 +1887,7 @@
         <v>103.77955086151603</v>
       </c>
     </row>
-    <row r="192" spans="1:2">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>350</v>
       </c>
@@ -1899,7 +1895,7 @@
         <v>99.323192616291436</v>
       </c>
     </row>
-    <row r="193" spans="1:2">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>349</v>
       </c>
@@ -1907,7 +1903,7 @@
         <v>101.58087180369945</v>
       </c>
     </row>
-    <row r="194" spans="1:2">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>348</v>
       </c>
@@ -1915,7 +1911,7 @@
         <v>102.57803458075169</v>
       </c>
     </row>
-    <row r="195" spans="1:2">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>347</v>
       </c>
@@ -1923,7 +1919,7 @@
         <v>107.00407030703786</v>
       </c>
     </row>
-    <row r="196" spans="1:2">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>346</v>
       </c>
@@ -1931,7 +1927,7 @@
         <v>112.08861199621839</v>
       </c>
     </row>
-    <row r="197" spans="1:2">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>345</v>
       </c>
@@ -1939,7 +1935,7 @@
         <v>116.3691481673648</v>
       </c>
     </row>
-    <row r="198" spans="1:2">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>344</v>
       </c>
@@ -1947,7 +1943,7 @@
         <v>119.92160688541222</v>
       </c>
     </row>
-    <row r="199" spans="1:2">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>343</v>
       </c>
@@ -1955,7 +1951,7 @@
         <v>122.45620806968293</v>
       </c>
     </row>
-    <row r="200" spans="1:2">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>342</v>
       </c>
@@ -1963,7 +1959,7 @@
         <v>120.2300828769483</v>
       </c>
     </row>
-    <row r="201" spans="1:2">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>341</v>
       </c>
@@ -1971,7 +1967,7 @@
         <v>121.10130455205207</v>
       </c>
     </row>
-    <row r="202" spans="1:2">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>340</v>
       </c>
@@ -1979,7 +1975,7 @@
         <v>121.51143194157747</v>
       </c>
     </row>
-    <row r="203" spans="1:2">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>339</v>
       </c>
@@ -1987,7 +1983,7 @@
         <v>124.97951726909319</v>
       </c>
     </row>
-    <row r="204" spans="1:2">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>338</v>
       </c>
@@ -1995,7 +1991,7 @@
         <v>124.97413124423173</v>
       </c>
     </row>
-    <row r="205" spans="1:2">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>337</v>
       </c>
@@ -2003,7 +1999,7 @@
         <v>121.13840086089225</v>
       </c>
     </row>
-    <row r="206" spans="1:2">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>336</v>
       </c>
@@ -2011,7 +2007,7 @@
         <v>120.42082222952142</v>
       </c>
     </row>
-    <row r="207" spans="1:2">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>335</v>
       </c>
@@ -2019,7 +2015,7 @@
         <v>118.81177482690961</v>
       </c>
     </row>
-    <row r="208" spans="1:2">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>334</v>
       </c>
@@ -2027,7 +2023,7 @@
         <v>115.11885022569608</v>
       </c>
     </row>
-    <row r="209" spans="1:2">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>333</v>
       </c>
@@ -2035,7 +2031,7 @@
         <v>109.77536387855179</v>
       </c>
     </row>
-    <row r="210" spans="1:2">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>332</v>
       </c>
@@ -2043,7 +2039,7 @@
         <v>101.57630523046731</v>
       </c>
     </row>
-    <row r="211" spans="1:2">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>331</v>
       </c>
@@ -2051,7 +2047,7 @@
         <v>99.694772859021029</v>
       </c>
     </row>
-    <row r="212" spans="1:2">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>330</v>
       </c>
@@ -2059,7 +2055,7 @@
         <v>98.568113467602615</v>
       </c>
     </row>
-    <row r="213" spans="1:2">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>329</v>
       </c>
@@ -2067,7 +2063,7 @@
         <v>97.388167871025189</v>
       </c>
     </row>
-    <row r="214" spans="1:2">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>328</v>
       </c>
@@ -2075,7 +2071,7 @@
         <v>92.020439178563649</v>
       </c>
     </row>
-    <row r="215" spans="1:2">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>327</v>
       </c>
@@ -2083,7 +2079,7 @@
         <v>85.767664386249947</v>
       </c>
     </row>
-    <row r="216" spans="1:2">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>326</v>
       </c>
@@ -2091,7 +2087,7 @@
         <v>78.789096617113046</v>
       </c>
     </row>
-    <row r="217" spans="1:2">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>325</v>
       </c>
@@ -2099,7 +2095,7 @@
         <v>71.06174685783769</v>
       </c>
     </row>
-    <row r="218" spans="1:2">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>324</v>
       </c>
@@ -2107,7 +2103,7 @@
         <v>63.048707725927187</v>
       </c>
     </row>
-    <row r="219" spans="1:2">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>323</v>
       </c>
@@ -2115,7 +2111,7 @@
         <v>50.918514297157806</v>
       </c>
     </row>
-    <row r="220" spans="1:2">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>322</v>
       </c>
@@ -2123,7 +2119,7 @@
         <v>38.646403102402068</v>
       </c>
     </row>
-    <row r="221" spans="1:2">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>321</v>
       </c>
@@ -2131,7 +2127,7 @@
         <v>26.129308840796487</v>
       </c>
     </row>
-    <row r="222" spans="1:2">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>320</v>
       </c>
@@ -2139,7 +2135,7 @@
         <v>13.352301158215166</v>
       </c>
     </row>
-    <row r="223" spans="1:2">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>319</v>
       </c>
@@ -2147,7 +2143,7 @@
         <v>5.1036397969311267</v>
       </c>
     </row>
-    <row r="224" spans="1:2">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>318</v>
       </c>
@@ -2155,7 +2151,7 @@
         <v>2.7740193709240226</v>
       </c>
     </row>
-    <row r="225" spans="1:2">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>317</v>
       </c>
@@ -2163,7 +2159,7 @@
         <v>0.90519623586072728</v>
       </c>
     </row>
-    <row r="226" spans="1:2">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>316</v>
       </c>
@@ -2171,7 +2167,7 @@
         <v>4.6005132711475198</v>
       </c>
     </row>
-    <row r="227" spans="1:2">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <v>315</v>
       </c>
@@ -2179,7 +2175,7 @@
         <v>8.5066850155796576</v>
       </c>
     </row>
-    <row r="228" spans="1:2">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>314</v>
       </c>
@@ -2187,7 +2183,7 @@
         <v>12.519447002888908</v>
       </c>
     </row>
-    <row r="229" spans="1:2">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>313</v>
       </c>
@@ -2195,7 +2191,7 @@
         <v>12.078578596505842</v>
       </c>
     </row>
-    <row r="230" spans="1:2">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>312</v>
       </c>
@@ -2203,7 +2199,7 @@
         <v>16.596995278268405</v>
       </c>
     </row>
-    <row r="231" spans="1:2">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>311</v>
       </c>
@@ -2211,7 +2207,7 @@
         <v>16.375162017057097</v>
       </c>
     </row>
-    <row r="232" spans="1:2">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>310</v>
       </c>
@@ -2219,7 +2215,7 @@
         <v>16.522693792247118</v>
       </c>
     </row>
-    <row r="233" spans="1:2">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>309</v>
       </c>
@@ -2227,7 +2223,7 @@
         <v>16.383277995559048</v>
       </c>
     </row>
-    <row r="234" spans="1:2">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>308</v>
       </c>
@@ -2235,7 +2231,7 @@
         <v>16.742374259175655</v>
       </c>
     </row>
-    <row r="235" spans="1:2">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <v>307</v>
       </c>
@@ -2243,7 +2239,7 @@
         <v>17.076622968776579</v>
       </c>
     </row>
-    <row r="236" spans="1:2">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <v>306</v>
       </c>
@@ -2251,7 +2247,7 @@
         <v>17.765517876263278</v>
       </c>
     </row>
-    <row r="237" spans="1:2">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <v>305</v>
       </c>
@@ -2259,7 +2255,7 @@
         <v>18.711143089914838</v>
       </c>
     </row>
-    <row r="238" spans="1:2">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <v>304</v>
       </c>
@@ -2267,7 +2263,7 @@
         <v>15.213181384387001</v>
       </c>
     </row>
-    <row r="239" spans="1:2">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <v>303</v>
       </c>
@@ -2275,7 +2271,7 @@
         <v>16.769291200285192</v>
       </c>
     </row>
-    <row r="240" spans="1:2">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <v>302</v>
       </c>
@@ -2283,7 +2279,7 @@
         <v>13.270016741056962</v>
       </c>
     </row>
-    <row r="241" spans="1:2">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
         <v>301</v>
       </c>
@@ -2291,7 +2287,7 @@
         <v>14.78083239123403</v>
       </c>
     </row>
-    <row r="242" spans="1:2">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
         <v>300</v>
       </c>
@@ -2299,7 +2295,7 @@
         <v>16.195794822786727</v>
       </c>
     </row>
-    <row r="243" spans="1:2">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
         <v>299</v>
       </c>
@@ -2307,7 +2303,7 @@
         <v>24.636476113214723</v>
       </c>
     </row>
-    <row r="244" spans="1:2">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
         <v>298</v>
       </c>
@@ -2315,7 +2311,7 @@
         <v>28.934013569305822</v>
       </c>
     </row>
-    <row r="245" spans="1:2">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
         <v>297</v>
       </c>
@@ -2323,7 +2319,7 @@
         <v>34.139829676054262</v>
       </c>
     </row>
-    <row r="246" spans="1:2">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
         <v>296</v>
       </c>
@@ -2331,7 +2327,7 @@
         <v>33.904670110017065</v>
       </c>
     </row>
-    <row r="247" spans="1:2">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
         <v>295</v>
       </c>
@@ -2339,7 +2335,7 @@
         <v>26.687567362525456</v>
       </c>
     </row>
-    <row r="248" spans="1:2">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
         <v>294</v>
       </c>
@@ -2347,7 +2343,7 @@
         <v>28.883733980552243</v>
       </c>
     </row>
-    <row r="249" spans="1:2">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
         <v>293</v>
       </c>
@@ -2355,7 +2351,7 @@
         <v>37.078481158512858</v>
       </c>
     </row>
-    <row r="250" spans="1:2">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
         <v>292</v>
       </c>
@@ -2363,7 +2359,7 @@
         <v>48.900486128680697</v>
       </c>
     </row>
-    <row r="251" spans="1:2">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
         <v>291</v>
       </c>
@@ -2371,7 +2367,7 @@
         <v>56.35657070878505</v>
       </c>
     </row>
-    <row r="252" spans="1:2">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
         <v>290</v>
       </c>
@@ -2379,7 +2375,7 @@
         <v>66.716254999589225</v>
       </c>
     </row>
-    <row r="253" spans="1:2">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
         <v>289</v>
       </c>
@@ -2387,7 +2383,7 @@
         <v>78.745182221874458</v>
       </c>
     </row>
-    <row r="254" spans="1:2">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
         <v>288</v>
       </c>
@@ -2395,7 +2391,7 @@
         <v>86.336176997839303</v>
       </c>
     </row>
-    <row r="255" spans="1:2">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
         <v>287</v>
       </c>
@@ -2403,7 +2399,7 @@
         <v>94.416127402580159</v>
       </c>
     </row>
-    <row r="256" spans="1:2">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
         <v>286</v>
       </c>
@@ -2411,7 +2407,7 @@
         <v>96.70249321040248</v>
       </c>
     </row>
-    <row r="257" spans="1:2">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
         <v>285</v>
       </c>
@@ -2419,7 +2415,7 @@
         <v>98.151741048073006</v>
       </c>
     </row>
-    <row r="258" spans="1:2">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
         <v>284</v>
       </c>
@@ -2427,7 +2423,7 @@
         <v>99.177748616911344</v>
       </c>
     </row>
-    <row r="259" spans="1:2">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
         <v>283</v>
       </c>
@@ -2435,7 +2431,7 @@
         <v>98.257445412482468</v>
       </c>
     </row>
-    <row r="260" spans="1:2">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
         <v>282</v>
       </c>
@@ -2443,7 +2439,7 @@
         <v>93.02443463199883</v>
       </c>
     </row>
-    <row r="261" spans="1:2">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
         <v>281</v>
       </c>
@@ -2451,7 +2447,7 @@
         <v>96.2479192760035</v>
       </c>
     </row>
-    <row r="262" spans="1:2">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
         <v>280</v>
       </c>
@@ -2459,7 +2455,7 @@
         <v>103.83912857230207</v>
       </c>
     </row>
-    <row r="263" spans="1:2">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
         <v>279</v>
       </c>
@@ -2467,7 +2463,7 @@
         <v>106.00137976862101</v>
       </c>
     </row>
-    <row r="264" spans="1:2">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
         <v>278</v>
       </c>
@@ -2475,7 +2471,7 @@
         <v>112.1794208879614</v>
       </c>
     </row>
-    <row r="265" spans="1:2">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
         <v>277</v>
       </c>
@@ -2483,7 +2479,7 @@
         <v>113.32909579189408</v>
       </c>
     </row>
-    <row r="266" spans="1:2">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
         <v>276</v>
       </c>
@@ -2491,7 +2487,7 @@
         <v>118.54480818186889</v>
       </c>
     </row>
-    <row r="267" spans="1:2">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
         <v>275</v>
       </c>
@@ -2499,7 +2495,7 @@
         <v>121.4166482580397</v>
       </c>
     </row>
-    <row r="268" spans="1:2">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
         <v>274</v>
       </c>
@@ -2507,7 +2503,7 @@
         <v>127.75902111130178</v>
       </c>
     </row>
-    <row r="269" spans="1:2">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
         <v>273</v>
       </c>
@@ -2515,7 +2511,7 @@
         <v>133.97982580773538</v>
       </c>
     </row>
-    <row r="270" spans="1:2">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
         <v>272</v>
       </c>
@@ -2523,7 +2519,7 @@
         <v>136.58813560246372</v>
       </c>
     </row>
-    <row r="271" spans="1:2">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
         <v>271</v>
       </c>
@@ -2531,7 +2527,7 @@
         <v>141.87391139343833</v>
       </c>
     </row>
-    <row r="272" spans="1:2">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
         <v>270</v>
       </c>
@@ -2539,7 +2535,7 @@
         <v>146.67079776248909</v>
       </c>
     </row>
-    <row r="273" spans="1:2">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
         <v>269</v>
       </c>
@@ -2547,7 +2543,7 @@
         <v>150.75365545279973</v>
       </c>
     </row>
-    <row r="274" spans="1:2">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
         <v>268</v>
       </c>
@@ -2555,7 +2551,7 @@
         <v>152.00254885178444</v>
       </c>
     </row>
-    <row r="275" spans="1:2">
+    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
         <v>267</v>
       </c>
@@ -2563,7 +2559,7 @@
         <v>149.780240360025</v>
       </c>
     </row>
-    <row r="276" spans="1:2">
+    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
         <v>266</v>
       </c>
@@ -2571,7 +2567,7 @@
         <v>150.03778226129771</v>
       </c>
     </row>
-    <row r="277" spans="1:2">
+    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
         <v>265</v>
       </c>
@@ -2579,7 +2575,7 @@
         <v>149.97532529286815</v>
       </c>
     </row>
-    <row r="278" spans="1:2">
+    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
         <v>264</v>
       </c>
@@ -2587,7 +2583,7 @@
         <v>148.36300888960818</v>
       </c>
     </row>
-    <row r="279" spans="1:2">
+    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
         <v>263</v>
       </c>
@@ -2595,7 +2591,7 @@
         <v>150.39086720459417</v>
       </c>
     </row>
-    <row r="280" spans="1:2">
+    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
         <v>262</v>
       </c>
@@ -2603,7 +2599,7 @@
         <v>151.53611252169728</v>
       </c>
     </row>
-    <row r="281" spans="1:2">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
         <v>261</v>
       </c>
@@ -2611,7 +2607,7 @@
         <v>151.70031160525184</v>
       </c>
     </row>
-    <row r="282" spans="1:2">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
         <v>260</v>
       </c>
@@ -2619,7 +2615,7 @@
         <v>151.37214819574612</v>
       </c>
     </row>
-    <row r="283" spans="1:2">
+    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
         <v>259</v>
       </c>
@@ -2627,7 +2623,7 @@
         <v>150.96669936173038</v>
       </c>
     </row>
-    <row r="284" spans="1:2">
+    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
         <v>258</v>
       </c>
@@ -2635,7 +2631,7 @@
         <v>150.10048843506931</v>
       </c>
     </row>
-    <row r="285" spans="1:2">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
         <v>257</v>
       </c>
@@ -2643,7 +2639,7 @@
         <v>144.96010537145486</v>
       </c>
     </row>
-    <row r="286" spans="1:2">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
         <v>256</v>
       </c>
@@ -2651,7 +2647,7 @@
         <v>141.58049603500282</v>
       </c>
     </row>
-    <row r="287" spans="1:2">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
         <v>255</v>
       </c>
@@ -2659,7 +2655,7 @@
         <v>136.08758436222908</v>
       </c>
     </row>
-    <row r="288" spans="1:2">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A288" s="1">
         <v>254</v>
       </c>
@@ -2667,7 +2663,7 @@
         <v>133.16416572099192</v>
       </c>
     </row>
-    <row r="289" spans="1:2">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A289" s="1">
         <v>253</v>
       </c>
@@ -2675,7 +2671,7 @@
         <v>139.40557180297773</v>
       </c>
     </row>
-    <row r="290" spans="1:2">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A290" s="1">
         <v>252</v>
       </c>
@@ -2683,7 +2679,7 @@
         <v>138.25244361230807</v>
       </c>
     </row>
-    <row r="291" spans="1:2">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A291" s="1">
         <v>251</v>
       </c>
@@ -2691,7 +2687,7 @@
         <v>120.29648917336425</v>
       </c>
     </row>
-    <row r="292" spans="1:2">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A292" s="1">
         <v>250</v>
       </c>
@@ -2699,7 +2695,7 @@
         <v>99.48756788584069</v>
       </c>
     </row>
-    <row r="293" spans="1:2">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A293" s="1">
         <v>249</v>
       </c>
@@ -2707,7 +2703,7 @@
         <v>74.646607543260956</v>
       </c>
     </row>
-    <row r="294" spans="1:2">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A294" s="1">
         <v>248</v>
       </c>
@@ -2715,7 +2711,7 @@
         <v>66.12685781516673</v>
       </c>
     </row>
-    <row r="295" spans="1:2">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A295" s="1">
         <v>247</v>
       </c>
@@ -2723,7 +2719,7 @@
         <v>54.430726764760223</v>
       </c>
     </row>
-    <row r="296" spans="1:2">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A296" s="1">
         <v>246</v>
       </c>
@@ -2731,7 +2727,7 @@
         <v>51.454793334759394</v>
       </c>
     </row>
-    <row r="297" spans="1:2">
+    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A297" s="1">
         <v>245</v>
       </c>
@@ -2739,7 +2735,7 @@
         <v>54.292250365395432</v>
       </c>
     </row>
-    <row r="298" spans="1:2">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A298" s="1">
         <v>244</v>
       </c>
@@ -2747,7 +2743,7 @@
         <v>58.826936094852982</v>
       </c>
     </row>
-    <row r="299" spans="1:2">
+    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A299" s="1">
         <v>243</v>
       </c>
@@ -2755,7 +2751,7 @@
         <v>62.7159465321242</v>
       </c>
     </row>
-    <row r="300" spans="1:2">
+    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A300" s="1">
         <v>242</v>
       </c>
@@ -2763,7 +2759,7 @@
         <v>66.237494375965284</v>
       </c>
     </row>
-    <row r="301" spans="1:2">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A301" s="1">
         <v>241</v>
       </c>
@@ -2771,7 +2767,7 @@
         <v>69.110909526739988</v>
       </c>
     </row>
-    <row r="302" spans="1:2">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A302" s="1">
         <v>240</v>
       </c>
@@ -2779,7 +2775,7 @@
         <v>71.397885122043746</v>
       </c>
     </row>
-    <row r="303" spans="1:2">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A303" s="1">
         <v>239</v>
       </c>
@@ -2787,7 +2783,7 @@
         <v>72.960192771492402</v>
       </c>
     </row>
-    <row r="304" spans="1:2">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A304" s="1">
         <v>238</v>
       </c>
@@ -2795,7 +2791,7 @@
         <v>73.155495297657112</v>
       </c>
     </row>
-    <row r="305" spans="1:2">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A305" s="1">
         <v>237</v>
       </c>
@@ -2803,7 +2799,7 @@
         <v>72.979325303497617</v>
       </c>
     </row>
-    <row r="306" spans="1:2">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A306" s="1">
         <v>236</v>
       </c>
@@ -2811,7 +2807,7 @@
         <v>71.513839536116137</v>
       </c>
     </row>
-    <row r="307" spans="1:2">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A307" s="1">
         <v>235</v>
       </c>
@@ -2819,7 +2815,7 @@
         <v>70.111274691168589</v>
       </c>
     </row>
-    <row r="308" spans="1:2">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A308" s="1">
         <v>234</v>
       </c>
@@ -2827,7 +2823,7 @@
         <v>68.144260191698478</v>
       </c>
     </row>
-    <row r="309" spans="1:2">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A309" s="1">
         <v>233</v>
       </c>
@@ -2835,7 +2831,7 @@
         <v>65.822179908930281</v>
       </c>
     </row>
-    <row r="310" spans="1:2">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A310" s="1">
         <v>232</v>
       </c>
@@ -2843,7 +2839,7 @@
         <v>63.5567980660459</v>
       </c>
     </row>
-    <row r="311" spans="1:2">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A311" s="1">
         <v>231</v>
       </c>
@@ -2851,7 +2847,7 @@
         <v>61.11782541176639</v>
       </c>
     </row>
-    <row r="312" spans="1:2">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A312" s="1">
         <v>230</v>
       </c>
@@ -2859,7 +2855,7 @@
         <v>58.826133611172544</v>
       </c>
     </row>
-    <row r="313" spans="1:2">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A313" s="1">
         <v>229</v>
       </c>
@@ -2867,7 +2863,7 @@
         <v>56.640126822810885</v>
       </c>
     </row>
-    <row r="314" spans="1:2">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A314" s="1">
         <v>228</v>
       </c>
@@ -2875,7 +2871,7 @@
         <v>54.501950023945113</v>
       </c>
     </row>
-    <row r="315" spans="1:2">
+    <row r="315" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A315" s="1">
         <v>227</v>
       </c>
@@ -2883,7 +2879,7 @@
         <v>52.437144807000031</v>
       </c>
     </row>
-    <row r="316" spans="1:2">
+    <row r="316" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A316" s="1">
         <v>226</v>
       </c>
@@ -2891,7 +2887,7 @@
         <v>50.74268966985786</v>
       </c>
     </row>
-    <row r="317" spans="1:2">
+    <row r="317" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A317" s="1">
         <v>225</v>
       </c>
@@ -2899,7 +2895,7 @@
         <v>49.366552983160631</v>
       </c>
     </row>
-    <row r="318" spans="1:2">
+    <row r="318" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A318" s="1">
         <v>224</v>
       </c>
@@ -2907,7 +2903,7 @@
         <v>47.98248178925617</v>
       </c>
     </row>
-    <row r="319" spans="1:2">
+    <row r="319" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A319" s="1">
         <v>223</v>
       </c>
@@ -2915,7 +2911,7 @@
         <v>45.849820004319298</v>
       </c>
     </row>
-    <row r="320" spans="1:2">
+    <row r="320" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A320" s="1">
         <v>222</v>
       </c>
@@ -2923,7 +2919,7 @@
         <v>43.360973167927369</v>
       </c>
     </row>
-    <row r="321" spans="1:2">
+    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A321" s="1">
         <v>221</v>
       </c>
@@ -2931,7 +2927,7 @@
         <v>41.903538439628008</v>
       </c>
     </row>
-    <row r="322" spans="1:2">
+    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A322" s="1">
         <v>220</v>
       </c>
@@ -2939,7 +2935,7 @@
         <v>40.47685438106847</v>
       </c>
     </row>
-    <row r="323" spans="1:2">
+    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A323" s="1">
         <v>219</v>
       </c>
@@ -2947,7 +2943,7 @@
         <v>44.56559317326262</v>
       </c>
     </row>
-    <row r="324" spans="1:2">
+    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A324" s="1">
         <v>218</v>
       </c>
@@ -2955,7 +2951,7 @@
         <v>46.749003567449158</v>
       </c>
     </row>
-    <row r="325" spans="1:2">
+    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A325" s="1">
         <v>217</v>
       </c>
@@ -2963,7 +2959,7 @@
         <v>48.671467984762025</v>
       </c>
     </row>
-    <row r="326" spans="1:2">
+    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A326" s="1">
         <v>216</v>
       </c>
@@ -2971,7 +2967,7 @@
         <v>50.508626258887759</v>
       </c>
     </row>
-    <row r="327" spans="1:2">
+    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A327" s="1">
         <v>215</v>
       </c>
@@ -2979,7 +2975,7 @@
         <v>52.3949455636956</v>
       </c>
     </row>
-    <row r="328" spans="1:2">
+    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A328" s="1">
         <v>214</v>
       </c>
@@ -2987,7 +2983,7 @@
         <v>54.362102509675843</v>
       </c>
     </row>
-    <row r="329" spans="1:2">
+    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A329" s="1">
         <v>213</v>
       </c>
@@ -2995,7 +2991,7 @@
         <v>56.315907335549468</v>
       </c>
     </row>
-    <row r="330" spans="1:2">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A330" s="1">
         <v>212</v>
       </c>
@@ -3003,7 +2999,7 @@
         <v>58.381299546535637</v>
       </c>
     </row>
-    <row r="331" spans="1:2">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A331" s="1">
         <v>211</v>
       </c>
@@ -3011,7 +3007,7 @@
         <v>60.660323637391187</v>
       </c>
     </row>
-    <row r="332" spans="1:2">
+    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A332" s="1">
         <v>210</v>
       </c>
@@ -3019,7 +3015,7 @@
         <v>63.282531200623119</v>
       </c>
     </row>
-    <row r="333" spans="1:2">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A333" s="1">
         <v>209</v>
       </c>
@@ -3027,7 +3023,7 @@
         <v>66.278291626727736</v>
       </c>
     </row>
-    <row r="334" spans="1:2">
+    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A334" s="1">
         <v>208</v>
       </c>
@@ -3035,7 +3031,7 @@
         <v>68.503928697494871</v>
       </c>
     </row>
-    <row r="335" spans="1:2">
+    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A335" s="1">
         <v>207</v>
       </c>
@@ -3043,7 +3039,7 @@
         <v>72.575548729037507</v>
       </c>
     </row>
-    <row r="336" spans="1:2">
+    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A336" s="1">
         <v>206</v>
       </c>
@@ -3051,7 +3047,7 @@
         <v>75.121971138963929</v>
       </c>
     </row>
-    <row r="337" spans="1:2">
+    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A337" s="1">
         <v>205</v>
       </c>
@@ -3059,7 +3055,7 @@
         <v>79.111217906494275</v>
       </c>
     </row>
-    <row r="338" spans="1:2">
+    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A338" s="1">
         <v>204</v>
       </c>
@@ -3067,7 +3063,7 @@
         <v>82.129248510610239</v>
       </c>
     </row>
-    <row r="339" spans="1:2">
+    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A339" s="1">
         <v>203</v>
       </c>
@@ -3075,7 +3071,7 @@
         <v>89.683897786420403</v>
       </c>
     </row>
-    <row r="340" spans="1:2">
+    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A340" s="1">
         <v>202</v>
       </c>
@@ -3083,7 +3079,7 @@
         <v>97.062251882745642</v>
       </c>
     </row>
-    <row r="341" spans="1:2">
+    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A341" s="1">
         <v>201</v>
       </c>
@@ -3091,7 +3087,7 @@
         <v>102.6388684214689</v>
       </c>
     </row>
-    <row r="342" spans="1:2">
+    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A342" s="1">
         <v>200</v>
       </c>
@@ -3099,7 +3095,7 @@
         <v>110.34461199893221</v>
       </c>
     </row>
-    <row r="343" spans="1:2">
+    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A343" s="1">
         <v>199</v>
       </c>
@@ -3107,7 +3103,7 @@
         <v>110.25259453508023</v>
       </c>
     </row>
-    <row r="344" spans="1:2">
+    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A344" s="1">
         <v>198</v>
       </c>
@@ -3115,7 +3111,7 @@
         <v>109.82970052067516</v>
       </c>
     </row>
-    <row r="345" spans="1:2">
+    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A345" s="1">
         <v>197</v>
       </c>
@@ -3123,7 +3119,7 @@
         <v>110.03923498111109</v>
       </c>
     </row>
-    <row r="346" spans="1:2">
+    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A346" s="1">
         <v>196</v>
       </c>
@@ -3131,7 +3127,7 @@
         <v>111.90128183836178</v>
       </c>
     </row>
-    <row r="347" spans="1:2">
+    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A347" s="1">
         <v>195</v>
       </c>
@@ -3139,7 +3135,7 @@
         <v>114.11425489847194</v>
       </c>
     </row>
-    <row r="348" spans="1:2">
+    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A348" s="1">
         <v>194</v>
       </c>
@@ -3147,7 +3143,7 @@
         <v>114.12079360109385</v>
       </c>
     </row>
-    <row r="349" spans="1:2">
+    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A349" s="1">
         <v>193</v>
       </c>
@@ -3155,7 +3151,7 @@
         <v>116.38009038600057</v>
       </c>
     </row>
-    <row r="350" spans="1:2">
+    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A350" s="1">
         <v>192</v>
       </c>
@@ -3163,7 +3159,7 @@
         <v>119.93726290810375</v>
       </c>
     </row>
-    <row r="351" spans="1:2">
+    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A351" s="1">
         <v>191</v>
       </c>
@@ -3171,7 +3167,7 @@
         <v>123.45652866891237</v>
       </c>
     </row>
-    <row r="352" spans="1:2">
+    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A352" s="1">
         <v>190</v>
       </c>
@@ -3179,7 +3175,7 @@
         <v>126.79502300111211</v>
       </c>
     </row>
-    <row r="353" spans="1:2">
+    <row r="353" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A353" s="1">
         <v>189</v>
       </c>
@@ -3187,7 +3183,7 @@
         <v>128.91854395429459</v>
       </c>
     </row>
-    <row r="354" spans="1:2">
+    <row r="354" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A354" s="1">
         <v>188</v>
       </c>
@@ -3195,7 +3191,7 @@
         <v>131.79839822779888</v>
       </c>
     </row>
-    <row r="355" spans="1:2">
+    <row r="355" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A355" s="1">
         <v>187</v>
       </c>
@@ -3203,7 +3199,7 @@
         <v>133.48998796563498</v>
       </c>
     </row>
-    <row r="356" spans="1:2">
+    <row r="356" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A356" s="1">
         <v>186</v>
       </c>
@@ -3211,7 +3207,7 @@
         <v>134.90712567550341</v>
       </c>
     </row>
-    <row r="357" spans="1:2">
+    <row r="357" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A357" s="1">
         <v>185</v>
       </c>
@@ -3219,7 +3215,7 @@
         <v>136.35588266993275</v>
       </c>
     </row>
-    <row r="358" spans="1:2">
+    <row r="358" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A358" s="1">
         <v>184</v>
       </c>
@@ -3227,7 +3223,7 @@
         <v>135.69327483094759</v>
       </c>
     </row>
-    <row r="359" spans="1:2">
+    <row r="359" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A359" s="1">
         <v>183</v>
       </c>
@@ -3235,7 +3231,7 @@
         <v>134.63741616616034</v>
       </c>
     </row>
-    <row r="360" spans="1:2">
+    <row r="360" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A360" s="1">
         <v>182</v>
       </c>
@@ -3243,7 +3239,7 @@
         <v>133.48079081469905</v>
       </c>
     </row>
-    <row r="361" spans="1:2">
+    <row r="361" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A361" s="1">
         <v>181</v>
       </c>
@@ -3251,7 +3247,7 @@
         <v>131.9940347149865</v>
       </c>
     </row>
-    <row r="362" spans="1:2">
+    <row r="362" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A362" s="1">
         <v>180</v>
       </c>
@@ -3259,7 +3255,7 @@
         <v>131.67656333022302</v>
       </c>
     </row>
-    <row r="363" spans="1:2">
+    <row r="363" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A363" s="1">
         <v>179</v>
       </c>
@@ -3267,7 +3263,7 @@
         <v>131.98420813639984</v>
       </c>
     </row>
-    <row r="364" spans="1:2">
+    <row r="364" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A364" s="1">
         <v>178</v>
       </c>
@@ -3275,7 +3271,7 @@
         <v>131.1359353083426</v>
       </c>
     </row>
-    <row r="365" spans="1:2">
+    <row r="365" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A365" s="1">
         <v>177</v>
       </c>
@@ -3283,7 +3279,7 @@
         <v>130.22897469258217</v>
       </c>
     </row>
-    <row r="366" spans="1:2">
+    <row r="366" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A366" s="1">
         <v>176</v>
       </c>
@@ -3291,7 +3287,7 @@
         <v>130.82818816345923</v>
       </c>
     </row>
-    <row r="367" spans="1:2">
+    <row r="367" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A367" s="1">
         <v>175</v>
       </c>
@@ -3299,7 +3295,7 @@
         <v>132.2721904072163</v>
       </c>
     </row>
-    <row r="368" spans="1:2">
+    <row r="368" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A368" s="1">
         <v>174</v>
       </c>
@@ -3307,7 +3303,7 @@
         <v>133.8215908930041</v>
       </c>
     </row>
-    <row r="369" spans="1:2">
+    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A369" s="1">
         <v>173</v>
       </c>
@@ -3315,7 +3311,7 @@
         <v>134.96748568161073</v>
       </c>
     </row>
-    <row r="370" spans="1:2">
+    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A370" s="1">
         <v>172</v>
       </c>
@@ -3323,7 +3319,7 @@
         <v>135.83691205061217</v>
       </c>
     </row>
-    <row r="371" spans="1:2">
+    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A371" s="1">
         <v>171</v>
       </c>
@@ -3331,7 +3327,7 @@
         <v>137.52853785334455</v>
       </c>
     </row>
-    <row r="372" spans="1:2">
+    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A372" s="1">
         <v>170</v>
       </c>
@@ -3339,7 +3335,7 @@
         <v>145.45300739555381</v>
       </c>
     </row>
-    <row r="373" spans="1:2">
+    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A373" s="1">
         <v>169</v>
       </c>
@@ -3347,7 +3343,7 @@
         <v>156.92522762985624</v>
       </c>
     </row>
-    <row r="374" spans="1:2">
+    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A374" s="1">
         <v>168</v>
       </c>
@@ -3355,7 +3351,7 @@
         <v>161.92541764603843</v>
       </c>
     </row>
-    <row r="375" spans="1:2">
+    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A375" s="1">
         <v>167</v>
       </c>
@@ -3363,7 +3359,7 @@
         <v>164.26588799787564</v>
       </c>
     </row>
-    <row r="376" spans="1:2">
+    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A376" s="1">
         <v>166</v>
       </c>
@@ -3371,7 +3367,7 @@
         <v>167.7986118085135</v>
       </c>
     </row>
-    <row r="377" spans="1:2">
+    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A377" s="1">
         <v>165</v>
       </c>
@@ -3379,7 +3375,7 @@
         <v>175.17451688166247</v>
       </c>
     </row>
-    <row r="378" spans="1:2">
+    <row r="378" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A378" s="1">
         <v>164</v>
       </c>
@@ -3387,7 +3383,7 @@
         <v>178.29878083425399</v>
       </c>
     </row>
-    <row r="379" spans="1:2">
+    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A379" s="1">
         <v>163</v>
       </c>
@@ -3395,7 +3391,7 @@
         <v>180.65700938487586</v>
       </c>
     </row>
-    <row r="380" spans="1:2">
+    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A380" s="1">
         <v>162</v>
       </c>
@@ -3403,7 +3399,7 @@
         <v>181.17392139737953</v>
       </c>
     </row>
-    <row r="381" spans="1:2">
+    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A381" s="1">
         <v>161</v>
       </c>
@@ -3411,7 +3407,7 @@
         <v>183.33176061101261</v>
       </c>
     </row>
-    <row r="382" spans="1:2">
+    <row r="382" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A382" s="1">
         <v>160</v>
       </c>
@@ -3419,7 +3415,7 @@
         <v>188.18182060322184</v>
       </c>
     </row>
-    <row r="383" spans="1:2">
+    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A383" s="1">
         <v>159</v>
       </c>
@@ -3427,7 +3423,7 @@
         <v>190.9976952928757</v>
       </c>
     </row>
-    <row r="384" spans="1:2">
+    <row r="384" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A384" s="1">
         <v>158</v>
       </c>
@@ -3435,7 +3431,7 @@
         <v>192.66009761181618</v>
       </c>
     </row>
-    <row r="385" spans="1:2">
+    <row r="385" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A385" s="1">
         <v>157</v>
       </c>
@@ -3443,7 +3439,7 @@
         <v>193.22778757235309</v>
       </c>
     </row>
-    <row r="386" spans="1:2">
+    <row r="386" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A386" s="1">
         <v>156</v>
       </c>
@@ -3451,7 +3447,7 @@
         <v>193.11433178679755</v>
       </c>
     </row>
-    <row r="387" spans="1:2">
+    <row r="387" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A387" s="1">
         <v>155</v>
       </c>
@@ -3459,7 +3455,7 @@
         <v>193.61335985231264</v>
       </c>
     </row>
-    <row r="388" spans="1:2">
+    <row r="388" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A388" s="1">
         <v>154</v>
       </c>
@@ -3467,7 +3463,7 @@
         <v>193.24040194638675</v>
       </c>
     </row>
-    <row r="389" spans="1:2">
+    <row r="389" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A389" s="1">
         <v>153</v>
       </c>
@@ -3475,7 +3471,7 @@
         <v>191.64765499639461</v>
       </c>
     </row>
-    <row r="390" spans="1:2">
+    <row r="390" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A390" s="1">
         <v>152</v>
       </c>
@@ -3483,7 +3479,7 @@
         <v>190.93273489453492</v>
       </c>
     </row>
-    <row r="391" spans="1:2">
+    <row r="391" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A391" s="1">
         <v>151</v>
       </c>
@@ -3491,7 +3487,7 @@
         <v>188.98820003607213</v>
       </c>
     </row>
-    <row r="392" spans="1:2">
+    <row r="392" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A392" s="1">
         <v>150</v>
       </c>
@@ -3499,7 +3495,7 @@
         <v>184.98013890119742</v>
       </c>
     </row>
-    <row r="393" spans="1:2">
+    <row r="393" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A393" s="1">
         <v>149</v>
       </c>
@@ -3507,7 +3503,7 @@
         <v>182.62341082841675</v>
       </c>
     </row>
-    <row r="394" spans="1:2">
+    <row r="394" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A394" s="1">
         <v>148</v>
       </c>
@@ -3515,7 +3511,7 @@
         <v>180.90205685957881</v>
       </c>
     </row>
-    <row r="395" spans="1:2">
+    <row r="395" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A395" s="1">
         <v>147</v>
       </c>
@@ -3523,7 +3519,7 @@
         <v>176.12482815788198</v>
       </c>
     </row>
-    <row r="396" spans="1:2">
+    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A396" s="1">
         <v>146</v>
       </c>
@@ -3531,7 +3527,7 @@
         <v>176.27657200307937</v>
       </c>
     </row>
-    <row r="397" spans="1:2">
+    <row r="397" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A397" s="1">
         <v>145</v>
       </c>
@@ -3539,7 +3535,7 @@
         <v>168.92492812647043</v>
       </c>
     </row>
-    <row r="398" spans="1:2">
+    <row r="398" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A398" s="1">
         <v>144</v>
       </c>
@@ -3547,7 +3543,7 @@
         <v>173.7529382339481</v>
       </c>
     </row>
-    <row r="399" spans="1:2">
+    <row r="399" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A399" s="1">
         <v>143</v>
       </c>
@@ -3555,7 +3551,7 @@
         <v>174.91476539309903</v>
       </c>
     </row>
-    <row r="400" spans="1:2">
+    <row r="400" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A400" s="1">
         <v>142</v>
       </c>
@@ -3563,7 +3559,7 @@
         <v>175.33040369224753</v>
       </c>
     </row>
-    <row r="401" spans="1:2">
+    <row r="401" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A401" s="1">
         <v>141</v>
       </c>
@@ -3571,7 +3567,7 @@
         <v>175.26567301123089</v>
       </c>
     </row>
-    <row r="402" spans="1:2">
+    <row r="402" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A402" s="1">
         <v>140</v>
       </c>
@@ -3579,7 +3575,7 @@
         <v>179.36884567454791</v>
       </c>
     </row>
-    <row r="403" spans="1:2">
+    <row r="403" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A403" s="1">
         <v>139</v>
       </c>
@@ -3587,7 +3583,7 @@
         <v>181.11468443004486</v>
       </c>
     </row>
-    <row r="404" spans="1:2">
+    <row r="404" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A404" s="1">
         <v>138</v>
       </c>
@@ -3595,7 +3591,7 @@
         <v>177.12412937344013</v>
       </c>
     </row>
-    <row r="405" spans="1:2">
+    <row r="405" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A405" s="1">
         <v>137</v>
       </c>
@@ -3603,7 +3599,7 @@
         <v>176.40667865468791</v>
       </c>
     </row>
-    <row r="406" spans="1:2">
+    <row r="406" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A406" s="1">
         <v>136</v>
       </c>
@@ -3611,7 +3607,7 @@
         <v>176.18010702977233</v>
       </c>
     </row>
-    <row r="407" spans="1:2">
+    <row r="407" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A407" s="1">
         <v>135</v>
       </c>
@@ -3619,7 +3615,7 @@
         <v>180.77446344717114</v>
       </c>
     </row>
-    <row r="408" spans="1:2">
+    <row r="408" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A408" s="1">
         <v>134</v>
       </c>
@@ -3627,7 +3623,7 @@
         <v>185.49658990955041</v>
       </c>
     </row>
-    <row r="409" spans="1:2">
+    <row r="409" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A409" s="1">
         <v>133</v>
       </c>
@@ -3635,7 +3631,7 @@
         <v>191.30069411560194</v>
       </c>
     </row>
-    <row r="410" spans="1:2">
+    <row r="410" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A410" s="1">
         <v>132</v>
       </c>
@@ -3643,7 +3639,7 @@
         <v>192.9882076624709</v>
       </c>
     </row>
-    <row r="411" spans="1:2">
+    <row r="411" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A411" s="1">
         <v>131</v>
       </c>
@@ -3651,7 +3647,7 @@
         <v>192.79394698259478</v>
       </c>
     </row>
-    <row r="412" spans="1:2">
+    <row r="412" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A412" s="1">
         <v>130</v>
       </c>
@@ -3659,7 +3655,7 @@
         <v>191.14773651804768</v>
       </c>
     </row>
-    <row r="413" spans="1:2">
+    <row r="413" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A413" s="1">
         <v>129</v>
       </c>
@@ -3667,7 +3663,7 @@
         <v>186.80041397238364</v>
       </c>
     </row>
-    <row r="414" spans="1:2">
+    <row r="414" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A414" s="1">
         <v>128</v>
       </c>
@@ -3675,7 +3671,7 @@
         <v>187.44156146832009</v>
       </c>
     </row>
-    <row r="415" spans="1:2">
+    <row r="415" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A415" s="1">
         <v>127</v>
       </c>
@@ -3683,7 +3679,7 @@
         <v>190.96976006159866</v>
       </c>
     </row>
-    <row r="416" spans="1:2">
+    <row r="416" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A416" s="1">
         <v>126</v>
       </c>
@@ -3691,7 +3687,7 @@
         <v>190.93676938320857</v>
       </c>
     </row>
-    <row r="417" spans="1:2">
+    <row r="417" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A417" s="1">
         <v>125</v>
       </c>
@@ -3699,7 +3695,7 @@
         <v>195.48032850267626</v>
       </c>
     </row>
-    <row r="418" spans="1:2">
+    <row r="418" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A418" s="1">
         <v>124</v>
       </c>
@@ -3707,7 +3703,7 @@
         <v>198.47049584283101</v>
       </c>
     </row>
-    <row r="419" spans="1:2">
+    <row r="419" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A419" s="1">
         <v>123</v>
       </c>
@@ -3715,7 +3711,7 @@
         <v>201.02168618400339</v>
       </c>
     </row>
-    <row r="420" spans="1:2">
+    <row r="420" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A420" s="1">
         <v>122</v>
       </c>
@@ -3723,7 +3719,7 @@
         <v>204.21965597438339</v>
       </c>
     </row>
-    <row r="421" spans="1:2">
+    <row r="421" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A421" s="1">
         <v>121</v>
       </c>
@@ -3731,7 +3727,7 @@
         <v>206.12810244704175</v>
       </c>
     </row>
-    <row r="422" spans="1:2">
+    <row r="422" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A422" s="1">
         <v>120</v>
       </c>
@@ -3739,7 +3735,7 @@
         <v>209.59658918957388</v>
       </c>
     </row>
-    <row r="423" spans="1:2">
+    <row r="423" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A423" s="1">
         <v>119</v>
       </c>
@@ -3747,7 +3743,7 @@
         <v>213.33068274925759</v>
       </c>
     </row>
-    <row r="424" spans="1:2">
+    <row r="424" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A424" s="1">
         <v>118</v>
       </c>
@@ -3755,7 +3751,7 @@
         <v>215.92559124923321</v>
       </c>
     </row>
-    <row r="425" spans="1:2">
+    <row r="425" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A425" s="1">
         <v>117</v>
       </c>
@@ -3763,7 +3759,7 @@
         <v>216.81541434750227</v>
       </c>
     </row>
-    <row r="426" spans="1:2">
+    <row r="426" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A426" s="1">
         <v>116</v>
       </c>
@@ -3771,7 +3767,7 @@
         <v>211.14838826481852</v>
       </c>
     </row>
-    <row r="427" spans="1:2">
+    <row r="427" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A427" s="1">
         <v>115</v>
       </c>
@@ -3779,7 +3775,7 @@
         <v>210.81745571004086</v>
       </c>
     </row>
-    <row r="428" spans="1:2">
+    <row r="428" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A428" s="1">
         <v>114</v>
       </c>
@@ -3787,7 +3783,7 @@
         <v>209.05240835804915</v>
       </c>
     </row>
-    <row r="429" spans="1:2">
+    <row r="429" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A429" s="1">
         <v>113</v>
       </c>
@@ -3795,7 +3791,7 @@
         <v>204.78698581524296</v>
       </c>
     </row>
-    <row r="430" spans="1:2">
+    <row r="430" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A430" s="1">
         <v>112</v>
       </c>
@@ -3803,7 +3799,7 @@
         <v>200.5208613691826</v>
       </c>
     </row>
-    <row r="431" spans="1:2">
+    <row r="431" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A431" s="1">
         <v>111</v>
       </c>
@@ -3811,7 +3807,7 @@
         <v>203.06719952907167</v>
       </c>
     </row>
-    <row r="432" spans="1:2">
+    <row r="432" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A432" s="1">
         <v>110</v>
       </c>
@@ -3819,7 +3815,7 @@
         <v>200.58862898481252</v>
       </c>
     </row>
-    <row r="433" spans="1:2">
+    <row r="433" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A433" s="1">
         <v>109</v>
       </c>
@@ -3827,7 +3823,7 @@
         <v>199.14305379658737</v>
       </c>
     </row>
-    <row r="434" spans="1:2">
+    <row r="434" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A434" s="1">
         <v>108</v>
       </c>
@@ -3835,7 +3831,7 @@
         <v>198.35890262244865</v>
       </c>
     </row>
-    <row r="435" spans="1:2">
+    <row r="435" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A435" s="1">
         <v>107</v>
       </c>
@@ -3843,7 +3839,7 @@
         <v>197.84648975987341</v>
       </c>
     </row>
-    <row r="436" spans="1:2">
+    <row r="436" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A436" s="1">
         <v>106</v>
       </c>
@@ -3851,7 +3847,7 @@
         <v>197.52287386636695</v>
       </c>
     </row>
-    <row r="437" spans="1:2">
+    <row r="437" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A437" s="1">
         <v>105</v>
       </c>
@@ -3859,7 +3855,7 @@
         <v>197.18545030625907</v>
       </c>
     </row>
-    <row r="438" spans="1:2">
+    <row r="438" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A438" s="1">
         <v>104</v>
       </c>
@@ -3867,7 +3863,7 @@
         <v>199.48990787016632</v>
       </c>
     </row>
-    <row r="439" spans="1:2">
+    <row r="439" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A439" s="1">
         <v>103</v>
       </c>
@@ -3875,7 +3871,7 @@
         <v>198.96831893046422</v>
       </c>
     </row>
-    <row r="440" spans="1:2">
+    <row r="440" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A440" s="1">
         <v>102</v>
       </c>
@@ -3883,7 +3879,7 @@
         <v>201.18312959696851</v>
       </c>
     </row>
-    <row r="441" spans="1:2">
+    <row r="441" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A441" s="1">
         <v>101</v>
       </c>
@@ -3891,7 +3887,7 @@
         <v>200.96157342380894</v>
       </c>
     </row>
-    <row r="442" spans="1:2">
+    <row r="442" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A442" s="1">
         <v>100</v>
       </c>
@@ -3899,7 +3895,7 @@
         <v>202.72351080949096</v>
       </c>
     </row>
-    <row r="443" spans="1:2">
+    <row r="443" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A443" s="1">
         <v>99</v>
       </c>
@@ -3907,7 +3903,7 @@
         <v>203.57578170336768</v>
       </c>
     </row>
-    <row r="444" spans="1:2">
+    <row r="444" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A444" s="1">
         <v>98</v>
       </c>
@@ -3915,7 +3911,7 @@
         <v>203.15378885313521</v>
       </c>
     </row>
-    <row r="445" spans="1:2">
+    <row r="445" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A445" s="1">
         <v>97</v>
       </c>
@@ -3923,7 +3919,7 @@
         <v>202.99631167423951</v>
       </c>
     </row>
-    <row r="446" spans="1:2">
+    <row r="446" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A446" s="1">
         <v>96</v>
       </c>
@@ -3931,7 +3927,7 @@
         <v>203.47806256373681</v>
       </c>
     </row>
-    <row r="447" spans="1:2">
+    <row r="447" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A447" s="1">
         <v>95</v>
       </c>
@@ -3939,7 +3935,7 @@
         <v>204.67664313479079</v>
       </c>
     </row>
-    <row r="448" spans="1:2">
+    <row r="448" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A448" s="1">
         <v>94</v>
       </c>
@@ -3947,7 +3943,7 @@
         <v>206.47392941148453</v>
       </c>
     </row>
-    <row r="449" spans="1:2">
+    <row r="449" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A449" s="1">
         <v>93</v>
       </c>
@@ -3955,7 +3951,7 @@
         <v>208.63252735933446</v>
       </c>
     </row>
-    <row r="450" spans="1:2">
+    <row r="450" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A450" s="1">
         <v>92</v>
       </c>
@@ -3963,7 +3959,7 @@
         <v>210.76310394567665</v>
       </c>
     </row>
-    <row r="451" spans="1:2">
+    <row r="451" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A451" s="1">
         <v>91</v>
       </c>
@@ -3971,7 +3967,7 @@
         <v>211.40553889200945</v>
       </c>
     </row>
-    <row r="452" spans="1:2">
+    <row r="452" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A452" s="1">
         <v>90</v>
       </c>
@@ -3979,7 +3975,7 @@
         <v>210.36896672524995</v>
       </c>
     </row>
-    <row r="453" spans="1:2">
+    <row r="453" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A453" s="1">
         <v>89</v>
       </c>
@@ -3987,7 +3983,7 @@
         <v>209.38430230094073</v>
       </c>
     </row>
-    <row r="454" spans="1:2">
+    <row r="454" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A454" s="1">
         <v>88</v>
       </c>
@@ -3995,7 +3991,7 @@
         <v>208.74968764573347</v>
       </c>
     </row>
-    <row r="455" spans="1:2">
+    <row r="455" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A455" s="1">
         <v>87</v>
       </c>
@@ -4003,7 +3999,7 @@
         <v>207.53077872990409</v>
       </c>
     </row>
-    <row r="456" spans="1:2">
+    <row r="456" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A456" s="1">
         <v>86</v>
       </c>
@@ -4011,7 +4007,7 @@
         <v>206.60929748804196</v>
       </c>
     </row>
-    <row r="457" spans="1:2">
+    <row r="457" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A457" s="1">
         <v>85</v>
       </c>
@@ -4019,7 +4015,7 @@
         <v>206.03904332639735</v>
       </c>
     </row>
-    <row r="458" spans="1:2">
+    <row r="458" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A458" s="1">
         <v>84</v>
       </c>
@@ -4027,7 +4023,7 @@
         <v>206.32711303754562</v>
       </c>
     </row>
-    <row r="459" spans="1:2">
+    <row r="459" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A459" s="1">
         <v>83</v>
       </c>
@@ -4035,7 +4031,7 @@
         <v>205.74875898345468</v>
       </c>
     </row>
-    <row r="460" spans="1:2">
+    <row r="460" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A460" s="1">
         <v>82</v>
       </c>
@@ -4043,7 +4039,7 @@
         <v>204.31058426807022</v>
       </c>
     </row>
-    <row r="461" spans="1:2">
+    <row r="461" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A461" s="1">
         <v>81</v>
       </c>
@@ -4051,7 +4047,7 @@
         <v>204.22717461264085</v>
       </c>
     </row>
-    <row r="462" spans="1:2">
+    <row r="462" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A462" s="1">
         <v>80</v>
       </c>
@@ -4059,7 +4055,7 @@
         <v>201.94429266944056</v>
       </c>
     </row>
-    <row r="463" spans="1:2">
+    <row r="463" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A463" s="1">
         <v>79</v>
       </c>
@@ -4067,7 +4063,7 @@
         <v>201.78906464851244</v>
       </c>
     </row>
-    <row r="464" spans="1:2">
+    <row r="464" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A464" s="1">
         <v>78</v>
       </c>
@@ -4075,7 +4071,7 @@
         <v>201.2339410920024</v>
       </c>
     </row>
-    <row r="465" spans="1:2">
+    <row r="465" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A465" s="1">
         <v>77</v>
       </c>
@@ -4083,7 +4079,7 @@
         <v>200.46530257242321</v>
       </c>
     </row>
-    <row r="466" spans="1:2">
+    <row r="466" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A466" s="1">
         <v>76</v>
       </c>
@@ -4091,7 +4087,7 @@
         <v>197.04890837922306</v>
       </c>
     </row>
-    <row r="467" spans="1:2">
+    <row r="467" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A467" s="1">
         <v>75</v>
       </c>
@@ -4099,7 +4095,7 @@
         <v>195.66145324247623</v>
       </c>
     </row>
-    <row r="468" spans="1:2">
+    <row r="468" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A468" s="1">
         <v>74</v>
       </c>
@@ -4107,7 +4103,7 @@
         <v>194.06195354860247</v>
       </c>
     </row>
-    <row r="469" spans="1:2">
+    <row r="469" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A469" s="1">
         <v>73</v>
       </c>
@@ -4115,7 +4111,7 @@
         <v>192.19386232885353</v>
       </c>
     </row>
-    <row r="470" spans="1:2">
+    <row r="470" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A470" s="1">
         <v>72</v>
       </c>
@@ -4123,7 +4119,7 @@
         <v>190.8177471734725</v>
       </c>
     </row>
-    <row r="471" spans="1:2">
+    <row r="471" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A471" s="1">
         <v>71</v>
       </c>
@@ -4131,7 +4127,7 @@
         <v>189.93416476678721</v>
       </c>
     </row>
-    <row r="472" spans="1:2">
+    <row r="472" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A472" s="1">
         <v>70</v>
       </c>
@@ -4139,7 +4135,7 @@
         <v>189.25541938940947</v>
       </c>
     </row>
-    <row r="473" spans="1:2">
+    <row r="473" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A473" s="1">
         <v>69</v>
       </c>
@@ -4147,7 +4143,7 @@
         <v>188.84776767975947</v>
       </c>
     </row>
-    <row r="474" spans="1:2">
+    <row r="474" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A474" s="1">
         <v>68</v>
       </c>
@@ -4155,7 +4151,7 @@
         <v>188.41975759982003</v>
       </c>
     </row>
-    <row r="475" spans="1:2">
+    <row r="475" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A475" s="1">
         <v>67</v>
       </c>
@@ -4163,7 +4159,7 @@
         <v>187.87497122144796</v>
       </c>
     </row>
-    <row r="476" spans="1:2">
+    <row r="476" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A476" s="1">
         <v>66</v>
       </c>
@@ -4171,7 +4167,7 @@
         <v>192.76051665059205</v>
       </c>
     </row>
-    <row r="477" spans="1:2">
+    <row r="477" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A477" s="1">
         <v>65</v>
       </c>
@@ -4179,7 +4175,7 @@
         <v>196.19227378155011</v>
       </c>
     </row>
-    <row r="478" spans="1:2">
+    <row r="478" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A478" s="1">
         <v>64</v>
       </c>
@@ -4187,7 +4183,7 @@
         <v>191.99842347671526</v>
       </c>
     </row>
-    <row r="479" spans="1:2">
+    <row r="479" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A479" s="1">
         <v>63</v>
       </c>
@@ -4195,7 +4191,7 @@
         <v>192.97200148521043</v>
       </c>
     </row>
-    <row r="480" spans="1:2">
+    <row r="480" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A480" s="1">
         <v>62</v>
       </c>
@@ -4203,7 +4199,7 @@
         <v>195.87882841210561</v>
       </c>
     </row>
-    <row r="481" spans="1:2">
+    <row r="481" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A481" s="1">
         <v>61</v>
       </c>
@@ -4211,7 +4207,7 @@
         <v>196.54050876524238</v>
       </c>
     </row>
-    <row r="482" spans="1:2">
+    <row r="482" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A482" s="1">
         <v>60</v>
       </c>
@@ -4219,7 +4215,7 @@
         <v>197.31580503911283</v>
       </c>
     </row>
-    <row r="483" spans="1:2">
+    <row r="483" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A483" s="1">
         <v>59</v>
       </c>
@@ -4227,7 +4223,7 @@
         <v>198.08482098547989</v>
       </c>
     </row>
-    <row r="484" spans="1:2">
+    <row r="484" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A484" s="1">
         <v>58</v>
       </c>
@@ -4235,7 +4231,7 @@
         <v>198.90224517436832</v>
       </c>
     </row>
-    <row r="485" spans="1:2">
+    <row r="485" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A485" s="1">
         <v>57</v>
       </c>
@@ -4243,7 +4239,7 @@
         <v>199.88488642693187</v>
       </c>
     </row>
-    <row r="486" spans="1:2">
+    <row r="486" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A486" s="1">
         <v>56</v>
       </c>
@@ -4251,7 +4247,7 @@
         <v>203.56578383123704</v>
       </c>
     </row>
-    <row r="487" spans="1:2">
+    <row r="487" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A487" s="1">
         <v>55</v>
       </c>
@@ -4259,7 +4255,7 @@
         <v>204.70823982656168</v>
       </c>
     </row>
-    <row r="488" spans="1:2">
+    <row r="488" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A488" s="1">
         <v>54</v>
       </c>
@@ -4267,7 +4263,7 @@
         <v>206.09744831511514</v>
       </c>
     </row>
-    <row r="489" spans="1:2">
+    <row r="489" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A489" s="1">
         <v>53</v>
       </c>
@@ -4275,7 +4271,7 @@
         <v>207.73790639281671</v>
       </c>
     </row>
-    <row r="490" spans="1:2">
+    <row r="490" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A490" s="1">
         <v>52</v>
       </c>
@@ -4283,7 +4279,7 @@
         <v>209.12834134542101</v>
       </c>
     </row>
-    <row r="491" spans="1:2">
+    <row r="491" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A491" s="1">
         <v>51</v>
       </c>
@@ -4291,7 +4287,7 @@
         <v>209.24884269226411</v>
       </c>
     </row>
-    <row r="492" spans="1:2">
+    <row r="492" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A492" s="1">
         <v>50</v>
       </c>
@@ -4299,7 +4295,7 @@
         <v>208.56043035161878</v>
       </c>
     </row>
-    <row r="493" spans="1:2">
+    <row r="493" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A493" s="1">
         <v>49</v>
       </c>
@@ -4307,7 +4303,7 @@
         <v>206.52027430255916</v>
       </c>
     </row>
-    <row r="494" spans="1:2">
+    <row r="494" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A494" s="1">
         <v>48</v>
       </c>
@@ -4315,7 +4311,7 @@
         <v>203.90469532970889</v>
       </c>
     </row>
-    <row r="495" spans="1:2">
+    <row r="495" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A495" s="1">
         <v>47</v>
       </c>
@@ -4323,7 +4319,7 @@
         <v>200.63360797131358</v>
       </c>
     </row>
-    <row r="496" spans="1:2">
+    <row r="496" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A496" s="1">
         <v>46</v>
       </c>
@@ -4331,7 +4327,7 @@
         <v>197.23788445876176</v>
       </c>
     </row>
-    <row r="497" spans="1:2">
+    <row r="497" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A497" s="1">
         <v>45</v>
       </c>
@@ -4339,7 +4335,7 @@
         <v>195.82381046432488</v>
       </c>
     </row>
-    <row r="498" spans="1:2">
+    <row r="498" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A498" s="1">
         <v>44</v>
       </c>
@@ -4347,7 +4343,7 @@
         <v>195.2765673183581</v>
       </c>
     </row>
-    <row r="499" spans="1:2">
+    <row r="499" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A499" s="1">
         <v>43</v>
       </c>
@@ -4355,7 +4351,7 @@
         <v>195.85075903471048</v>
       </c>
     </row>
-    <row r="500" spans="1:2">
+    <row r="500" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A500" s="1">
         <v>42</v>
       </c>
@@ -4363,7 +4359,7 @@
         <v>198.06582764633299</v>
       </c>
     </row>
-    <row r="501" spans="1:2">
+    <row r="501" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A501" s="1">
         <v>41</v>
       </c>
@@ -4371,7 +4367,7 @@
         <v>192.99794009658982</v>
       </c>
     </row>
-    <row r="502" spans="1:2">
+    <row r="502" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A502" s="1">
         <v>40</v>
       </c>
@@ -4379,7 +4375,7 @@
         <v>193.04600321907918</v>
       </c>
     </row>
-    <row r="503" spans="1:2">
+    <row r="503" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A503" s="1">
         <v>39</v>
       </c>
@@ -4387,7 +4383,7 @@
         <v>192.77217650559481</v>
       </c>
     </row>
-    <row r="504" spans="1:2">
+    <row r="504" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A504" s="1">
         <v>38</v>
       </c>
@@ -4395,7 +4391,7 @@
         <v>189.01346172323647</v>
       </c>
     </row>
-    <row r="505" spans="1:2">
+    <row r="505" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A505" s="1">
         <v>37</v>
       </c>
@@ -4403,7 +4399,7 @@
         <v>184.22529149554836</v>
       </c>
     </row>
-    <row r="506" spans="1:2">
+    <row r="506" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A506" s="1">
         <v>36</v>
       </c>
@@ -4411,7 +4407,7 @@
         <v>172.98728399660604</v>
       </c>
     </row>
-    <row r="507" spans="1:2">
+    <row r="507" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A507" s="1">
         <v>35</v>
       </c>
@@ -4419,7 +4415,7 @@
         <v>176.6749279918707</v>
       </c>
     </row>
-    <row r="508" spans="1:2">
+    <row r="508" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A508" s="1">
         <v>34</v>
       </c>
@@ -4427,7 +4423,7 @@
         <v>167.93081870322396</v>
       </c>
     </row>
-    <row r="509" spans="1:2">
+    <row r="509" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A509" s="1">
         <v>33</v>
       </c>
@@ -4435,7 +4431,7 @@
         <v>148.04457967468966</v>
       </c>
     </row>
-    <row r="510" spans="1:2">
+    <row r="510" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A510" s="1">
         <v>32</v>
       </c>
@@ -4443,7 +4439,7 @@
         <v>155.5773974072288</v>
       </c>
     </row>
-    <row r="511" spans="1:2">
+    <row r="511" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A511" s="1">
         <v>31</v>
       </c>
@@ -4451,7 +4447,7 @@
         <v>142.33282836336255</v>
       </c>
     </row>
-    <row r="512" spans="1:2">
+    <row r="512" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A512" s="1">
         <v>30</v>
       </c>
@@ -4459,7 +4455,7 @@
         <v>151.71369749470139</v>
       </c>
     </row>
-    <row r="513" spans="1:2">
+    <row r="513" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A513" s="1">
         <v>29</v>
       </c>
@@ -4467,7 +4463,7 @@
         <v>144.15121694487496</v>
       </c>
     </row>
-    <row r="514" spans="1:2">
+    <row r="514" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A514" s="1">
         <v>28</v>
       </c>
@@ -4475,7 +4471,7 @@
         <v>130.46892112597615</v>
       </c>
     </row>
-    <row r="515" spans="1:2">
+    <row r="515" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A515" s="1">
         <v>27</v>
       </c>
@@ -4483,7 +4479,7 @@
         <v>144.21458987517332</v>
       </c>
     </row>
-    <row r="516" spans="1:2">
+    <row r="516" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A516" s="1">
         <v>26</v>
       </c>
@@ -4491,7 +4487,7 @@
         <v>145.88708308146136</v>
       </c>
     </row>
-    <row r="517" spans="1:2">
+    <row r="517" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A517" s="1">
         <v>25</v>
       </c>
@@ -4499,7 +4495,7 @@
         <v>147.12809829846699</v>
       </c>
     </row>
-    <row r="518" spans="1:2">
+    <row r="518" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A518" s="1">
         <v>24</v>
       </c>
@@ -4507,7 +4503,7 @@
         <v>137.90531918113444</v>
       </c>
     </row>
-    <row r="519" spans="1:2">
+    <row r="519" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A519" s="1">
         <v>23</v>
       </c>
@@ -4515,7 +4511,7 @@
         <v>118.53556839281619</v>
       </c>
     </row>
-    <row r="520" spans="1:2">
+    <row r="520" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A520" s="1">
         <v>22</v>
       </c>
@@ -4523,7 +4519,7 @@
         <v>128.46144155694566</v>
       </c>
     </row>
-    <row r="521" spans="1:2">
+    <row r="521" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A521" s="1">
         <v>21</v>
       </c>
@@ -4531,7 +4527,7 @@
         <v>113.74492203349995</v>
       </c>
     </row>
-    <row r="522" spans="1:2">
+    <row r="522" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A522" s="1">
         <v>20</v>
       </c>
@@ -4539,7 +4535,7 @@
         <v>108.54238309388708</v>
       </c>
     </row>
-    <row r="523" spans="1:2">
+    <row r="523" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A523" s="1">
         <v>19</v>
       </c>
@@ -4547,7 +4543,7 @@
         <v>101.36685939913257</v>
       </c>
     </row>
-    <row r="524" spans="1:2">
+    <row r="524" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A524" s="1">
         <v>18</v>
       </c>
@@ -4555,7 +4551,7 @@
         <v>94.858145960199465</v>
       </c>
     </row>
-    <row r="525" spans="1:2">
+    <row r="525" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A525" s="1">
         <v>17</v>
       </c>
@@ -4563,7 +4559,7 @@
         <v>88.25809735042651</v>
       </c>
     </row>
-    <row r="526" spans="1:2">
+    <row r="526" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A526" s="1">
         <v>16</v>
       </c>
@@ -4571,7 +4567,7 @@
         <v>87.335487841310382</v>
       </c>
     </row>
-    <row r="527" spans="1:2">
+    <row r="527" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A527" s="1">
         <v>15</v>
       </c>
@@ -4579,7 +4575,7 @@
         <v>88.577545841831565</v>
       </c>
     </row>
-    <row r="528" spans="1:2">
+    <row r="528" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A528" s="1">
         <v>14</v>
       </c>
@@ -4587,7 +4583,7 @@
         <v>70.525325581574819</v>
       </c>
     </row>
-    <row r="529" spans="1:2">
+    <row r="529" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A529" s="1">
         <v>13</v>
       </c>
@@ -4595,7 +4591,7 @@
         <v>62.965233367278408</v>
       </c>
     </row>
-    <row r="530" spans="1:2">
+    <row r="530" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A530" s="1">
         <v>12</v>
       </c>
@@ -4603,7 +4599,7 @@
         <v>60.683219727645728</v>
       </c>
     </row>
-    <row r="531" spans="1:2">
+    <row r="531" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A531" s="1">
         <v>11</v>
       </c>
@@ -4611,7 +4607,7 @@
         <v>58.400513945461853</v>
       </c>
     </row>
-    <row r="532" spans="1:2">
+    <row r="532" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A532" s="1">
         <v>10</v>
       </c>
@@ -4619,7 +4615,7 @@
         <v>56.622304378338221</v>
       </c>
     </row>
-    <row r="533" spans="1:2">
+    <row r="533" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A533" s="1">
         <v>9</v>
       </c>
@@ -4627,7 +4623,7 @@
         <v>47.016347175178545</v>
       </c>
     </row>
-    <row r="534" spans="1:2">
+    <row r="534" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A534" s="1">
         <v>8</v>
       </c>
@@ -4635,7 +4631,7 @@
         <v>50.547620539399091</v>
       </c>
     </row>
-    <row r="535" spans="1:2">
+    <row r="535" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A535" s="1">
         <v>7</v>
       </c>
@@ -4643,7 +4639,7 @@
         <v>41.698418101630445</v>
       </c>
     </row>
-    <row r="536" spans="1:2">
+    <row r="536" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A536" s="1">
         <v>6</v>
       </c>
@@ -4651,7 +4647,7 @@
         <v>24.963740617951917</v>
       </c>
     </row>
-    <row r="537" spans="1:2">
+    <row r="537" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A537" s="1">
         <v>5</v>
       </c>
@@ -4659,7 +4655,7 @@
         <v>23.510174929959831</v>
       </c>
     </row>
-    <row r="538" spans="1:2">
+    <row r="538" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A538" s="1">
         <v>4</v>
       </c>
@@ -4667,7 +4663,7 @@
         <v>31.55724126642772</v>
       </c>
     </row>
-    <row r="539" spans="1:2">
+    <row r="539" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A539" s="1">
         <v>3</v>
       </c>
@@ -4675,7 +4671,7 @@
         <v>11.062539811251783</v>
       </c>
     </row>
-    <row r="540" spans="1:2">
+    <row r="540" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A540" s="1">
         <v>2</v>
       </c>
@@ -4683,7 +4679,7 @@
         <v>3.1224574130706935</v>
       </c>
     </row>
-    <row r="541" spans="1:2">
+    <row r="541" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A541" s="1">
         <v>1</v>
       </c>
@@ -4691,7 +4687,7 @@
         <v>-2.1812637713188172</v>
       </c>
     </row>
-    <row r="542" spans="1:2">
+    <row r="542" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A542" s="1">
         <v>0</v>
       </c>
@@ -4700,8 +4696,8 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:B546">
-    <sortCondition descending="1" ref="A2:A546"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:B542">
+    <sortCondition descending="1" ref="A1:A542"/>
   </sortState>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
